--- a/artfynd/A 33542-2021 artfynd.xlsx
+++ b/artfynd/A 33542-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33542-2021 artfynd.xlsx
+++ b/artfynd/A 33542-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>104023391</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544144.7679463385</v>
+        <v>544145</v>
       </c>
       <c r="R2" t="n">
-        <v>7093931.846950918</v>
+        <v>7093932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023379</v>
+        <v>104023388</v>
       </c>
       <c r="B3" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544417.6132623436</v>
+        <v>544192</v>
       </c>
       <c r="R3" t="n">
-        <v>7093770.51756385</v>
+        <v>7094020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +877,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,12 +905,7 @@
         <v>104023390</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544144.7679463385</v>
+        <v>544145</v>
       </c>
       <c r="R4" t="n">
-        <v>7093931.846950918</v>
+        <v>7093932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104023404</v>
+        <v>104023398</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543845.3978628411</v>
+        <v>543928</v>
       </c>
       <c r="R5" t="n">
-        <v>7094355.083793604</v>
+        <v>7094070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1112,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Lodyta</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,37 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104023403</v>
+        <v>104023387</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543844.5491681455</v>
+        <v>544148</v>
       </c>
       <c r="R6" t="n">
-        <v>7094352.875435072</v>
+        <v>7094025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med ungar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,11 +1230,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Lodyta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,32 +1250,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104023387</v>
+        <v>104023389</v>
       </c>
       <c r="B7" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1304,16 +1279,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen-Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544147.4095174377</v>
+        <v>544112</v>
       </c>
       <c r="R7" t="n">
-        <v>7094025.024694141</v>
+        <v>7093929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ungar</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,15 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104023383</v>
+        <v>104023404</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544401.2363577298</v>
+        <v>543846</v>
       </c>
       <c r="R8" t="n">
-        <v>7093901.214673067</v>
+        <v>7094355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,6 +1457,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Lodyta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1507,37 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104023401</v>
+        <v>104023407</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543908.6124882973</v>
+        <v>543798</v>
       </c>
       <c r="R9" t="n">
-        <v>7094332.690080668</v>
+        <v>7094387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1576,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,15 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104023377</v>
+        <v>104023401</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544403.1081541356</v>
+        <v>543909</v>
       </c>
       <c r="R10" t="n">
-        <v>7093893.332923243</v>
+        <v>7094333</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,37 +1714,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104023400</v>
+        <v>104023403</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1794,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543977.0867990054</v>
+        <v>543845</v>
       </c>
       <c r="R11" t="n">
-        <v>7094311.689439029</v>
+        <v>7094353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,7 +1808,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Lodyta</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,15 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104023402</v>
+        <v>104023400</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1915,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543833.5980712249</v>
+        <v>543977</v>
       </c>
       <c r="R12" t="n">
-        <v>7094349.646614409</v>
+        <v>7094312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1950,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,37 +1946,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104023388</v>
+        <v>104023402</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544191.4782816909</v>
+        <v>543833</v>
       </c>
       <c r="R13" t="n">
-        <v>7094019.497518884</v>
+        <v>7094350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,15 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104023384</v>
+        <v>104023399</v>
       </c>
       <c r="B14" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,21 +2073,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2157,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544403.8191363286</v>
+        <v>543974</v>
       </c>
       <c r="R14" t="n">
-        <v>7093905.205585789</v>
+        <v>7094189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2202,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,37 +2173,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104023399</v>
+        <v>104023382</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2273,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543973.5419088111</v>
+        <v>544411</v>
       </c>
       <c r="R15" t="n">
-        <v>7094188.634778374</v>
+        <v>7093922</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2308,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2318,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,6 +2277,576 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104023379</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544418</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7093770</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104023383</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544401</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7093901</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104023384</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544404</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7093905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104023377</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>544403</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7093893</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104023378</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544435</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7093756</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
